--- a/estoque_app/template_importacao_skus.xlsx
+++ b/estoque_app/template_importacao_skus.xlsx
@@ -423,15 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,20 +445,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>UNIDADE</t>
+          <t>SALDO_ATUAL</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>CATEGORIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LOCALIZACAO</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ESTOQUE_MINIMO</t>
         </is>

--- a/estoque_app/template_importacao_skus.xlsx
+++ b/estoque_app/template_importacao_skus.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SKUs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKUs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/estoque_app/template_importacao_skus.xlsx
+++ b/estoque_app/template_importacao_skus.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKUs" sheetId="1" r:id="R71f30b8a1d2b4a8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codigos" sheetId="1" r:id="R1292ee63fcd94158"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,7 +367,7 @@
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>SKU</x:v>
+        <x:v>COD</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
         <x:v>DESCRICAO</x:v>
